--- a/control_acceso/accesos_limpios_docentes.xlsx
+++ b/control_acceso/accesos_limpios_docentes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="128">
   <si>
     <t>nombre</t>
   </si>
@@ -232,184 +232,172 @@
     <t>1152701729</t>
   </si>
   <si>
-    <t>viernes , 01 de mayo</t>
-  </si>
-  <si>
-    <t>lunes , 04 de mayo</t>
-  </si>
-  <si>
-    <t>martes , 05 de mayo</t>
-  </si>
-  <si>
-    <t>miércoles , 06 de mayo</t>
-  </si>
-  <si>
-    <t>jueves , 07 de mayo</t>
-  </si>
-  <si>
-    <t>viernes , 08 de mayo</t>
-  </si>
-  <si>
-    <t>lunes , 11 de mayo</t>
-  </si>
-  <si>
-    <t>martes , 12 de mayo</t>
-  </si>
-  <si>
-    <t>miércoles , 13 de mayo</t>
-  </si>
-  <si>
-    <t>jueves , 14 de mayo</t>
-  </si>
-  <si>
-    <t>06:55</t>
+    <t>viernes , 15 de mayo</t>
+  </si>
+  <si>
+    <t>lunes , 18 de mayo</t>
+  </si>
+  <si>
+    <t>martes , 19 de mayo</t>
+  </si>
+  <si>
+    <t>miércoles , 20 de mayo</t>
+  </si>
+  <si>
+    <t>jueves , 21 de mayo</t>
+  </si>
+  <si>
+    <t>viernes , 22 de mayo</t>
+  </si>
+  <si>
+    <t>lunes , 25 de mayo</t>
+  </si>
+  <si>
+    <t>martes , 26 de mayo</t>
+  </si>
+  <si>
+    <t>miércoles , 27 de mayo</t>
+  </si>
+  <si>
+    <t>jueves , 28 de mayo</t>
+  </si>
+  <si>
+    <t>viernes , 29 de mayo</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>14:38</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>06:28</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>06:12</t>
   </si>
   <si>
     <t>06:18</t>
   </si>
   <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>07:03</t>
+    <t>06:44</t>
+  </si>
+  <si>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>06:37</t>
   </si>
   <si>
     <t>06:13</t>
   </si>
   <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>08:16</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>15:51</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
     <t>06:10</t>
   </si>
   <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>06:14</t>
-  </si>
-  <si>
-    <t>06:09</t>
+    <t>15:47</t>
+  </si>
+  <si>
+    <t>13:39</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>06:29</t>
   </si>
   <si>
     <t>06:07</t>
   </si>
   <si>
-    <t>06:12</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>06:29</t>
-  </si>
-  <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>06:52</t>
-  </si>
-  <si>
-    <t>07:02</t>
-  </si>
-  <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>06:36</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>08:48</t>
-  </si>
-  <si>
-    <t>08:19</t>
-  </si>
-  <si>
-    <t>07:01</t>
-  </si>
-  <si>
-    <t>06:54</t>
-  </si>
-  <si>
-    <t>06:28</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>07:00</t>
+    <t>15:34</t>
   </si>
   <si>
     <t>06:40</t>
   </si>
   <si>
+    <t>07:22</t>
+  </si>
+  <si>
+    <t>15:41</t>
+  </si>
+  <si>
     <t>06:43</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>07:21</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>15:36</t>
-  </si>
-  <si>
-    <t>15:31</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>15:43</t>
-  </si>
-  <si>
-    <t>07:18</t>
-  </si>
-  <si>
-    <t>07:11</t>
-  </si>
-  <si>
-    <t>11:03</t>
-  </si>
-  <si>
-    <t>07:05</t>
   </si>
 </sst>
 </file>
@@ -767,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D331"/>
+  <dimension ref="A1:D363"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -795,7 +783,7 @@
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -808,9 +796,6 @@
       <c r="C3" t="s">
         <v>73</v>
       </c>
-      <c r="D3" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
@@ -823,7 +808,7 @@
         <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -836,6 +821,9 @@
       <c r="C5" t="s">
         <v>75</v>
       </c>
+      <c r="D5" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
@@ -848,7 +836,7 @@
         <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -862,7 +850,7 @@
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -887,7 +875,7 @@
         <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -901,7 +889,7 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -914,19 +902,19 @@
       <c r="C11" t="s">
         <v>81</v>
       </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -937,10 +925,10 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -951,10 +939,7 @@
         <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -965,10 +950,10 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -979,10 +964,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -993,10 +975,10 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1007,10 +989,10 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1021,10 +1003,10 @@
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1035,10 +1017,10 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1049,29 +1031,35 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>81</v>
+      </c>
+      <c r="D22" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1082,10 +1070,7 @@
         <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1096,10 +1081,7 @@
         <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1110,10 +1092,10 @@
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1124,10 +1106,10 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1138,10 +1120,10 @@
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1152,10 +1134,10 @@
         <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1166,10 +1148,10 @@
         <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1180,49 +1162,46 @@
         <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="D31" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1233,10 +1212,10 @@
         <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1247,10 +1226,10 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1261,10 +1240,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1275,10 +1254,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1289,10 +1268,10 @@
         <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1303,10 +1282,10 @@
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1317,60 +1296,63 @@
         <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D41" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="D42" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>80</v>
+      </c>
+      <c r="D43" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1381,10 +1363,7 @@
         <v>42</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1395,10 +1374,7 @@
         <v>42</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
-      </c>
-      <c r="D47" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1409,10 +1385,10 @@
         <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1423,10 +1399,10 @@
         <v>42</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1437,10 +1413,10 @@
         <v>42</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1451,71 +1427,77 @@
         <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="D51" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>78</v>
+      </c>
+      <c r="D52" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>73</v>
+        <v>79</v>
+      </c>
+      <c r="D53" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1526,10 +1508,10 @@
         <v>43</v>
       </c>
       <c r="C57" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D57" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1540,10 +1522,10 @@
         <v>43</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1554,10 +1536,10 @@
         <v>43</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1568,10 +1550,10 @@
         <v>43</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D60" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1582,91 +1564,76 @@
         <v>43</v>
       </c>
       <c r="C61" t="s">
-        <v>81</v>
+        <v>76</v>
+      </c>
+      <c r="D61" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C62" t="s">
-        <v>72</v>
-      </c>
-      <c r="D62" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C63" t="s">
-        <v>73</v>
-      </c>
-      <c r="D63" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C64" t="s">
-        <v>74</v>
-      </c>
-      <c r="D64" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C65" t="s">
-        <v>75</v>
-      </c>
-      <c r="D65" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C66" t="s">
-        <v>76</v>
-      </c>
-      <c r="D66" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>77</v>
-      </c>
-      <c r="D67" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1677,10 +1644,7 @@
         <v>44</v>
       </c>
       <c r="C68" t="s">
-        <v>78</v>
-      </c>
-      <c r="D68" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1691,10 +1655,7 @@
         <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>79</v>
-      </c>
-      <c r="D69" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1705,10 +1666,7 @@
         <v>44</v>
       </c>
       <c r="C70" t="s">
-        <v>80</v>
-      </c>
-      <c r="D70" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1719,96 +1677,108 @@
         <v>44</v>
       </c>
       <c r="C71" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="D71" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" t="s">
-        <v>72</v>
+        <v>76</v>
+      </c>
+      <c r="D72" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="D73" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C74" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D74" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="D75" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C76" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D76" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D77" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C78" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D78" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1819,10 +1789,10 @@
         <v>45</v>
       </c>
       <c r="C79" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1833,10 +1803,7 @@
         <v>45</v>
       </c>
       <c r="C80" t="s">
-        <v>80</v>
-      </c>
-      <c r="D80" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1847,113 +1814,119 @@
         <v>45</v>
       </c>
       <c r="C81" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="D81" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C82" t="s">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="D82" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="D83" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C84" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D84" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C85" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C86" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D86" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C87" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D87" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C88" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D88" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C89" t="s">
-        <v>79</v>
-      </c>
-      <c r="D89" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1964,10 +1937,10 @@
         <v>46</v>
       </c>
       <c r="C90" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1978,43 +1951,49 @@
         <v>46</v>
       </c>
       <c r="C91" t="s">
-        <v>81</v>
+        <v>73</v>
+      </c>
+      <c r="D91" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C92" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D92" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C93" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="D93" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C94" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D94" t="s">
         <v>96</v>
@@ -2022,86 +2001,86 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C95" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D95" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C96" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C97" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D97" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C98" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D98" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C99" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D99" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C100" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D100" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2112,110 +2091,116 @@
         <v>47</v>
       </c>
       <c r="C101" t="s">
-        <v>81</v>
+        <v>72</v>
+      </c>
+      <c r="D101" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D102" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C103" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C104" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D104" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C105" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D105" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C106" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D106" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C107" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="D107" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C108" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D108" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C109" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D109" t="s">
         <v>95</v>
@@ -2223,46 +2208,49 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C110" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D110" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B111" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C111" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C112" t="s">
         <v>72</v>
       </c>
+      <c r="D112" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
@@ -2270,38 +2258,38 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C114" t="s">
         <v>74</v>
       </c>
       <c r="D114" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C115" t="s">
         <v>75</v>
       </c>
       <c r="D115" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C116" t="s">
         <v>76</v>
@@ -2312,1456 +2300,1444 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C117" t="s">
         <v>77</v>
       </c>
       <c r="D117" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C118" t="s">
         <v>78</v>
       </c>
       <c r="D118" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C119" t="s">
         <v>79</v>
       </c>
       <c r="D119" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C120" t="s">
         <v>80</v>
       </c>
       <c r="D120" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C121" t="s">
         <v>81</v>
       </c>
+      <c r="D121" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C122" t="s">
-        <v>72</v>
-      </c>
-      <c r="D122" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C123" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="D123" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C124" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="D124" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C125" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D125" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C126" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D126" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C127" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D127" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C128" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D128" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C129" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D129" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D130" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C131" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="D131" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C132" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C133" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B134" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C134" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D134" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B135" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C135" t="s">
-        <v>75</v>
-      </c>
-      <c r="D135" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B136" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C136" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D136" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B137" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C137" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D137" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B138" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C138" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D138" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B139" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C139" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D139" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B140" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C140" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D140" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B141" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C141" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="D141" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B142" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C142" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D142" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B143" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C143" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D143" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B144" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C144" t="s">
-        <v>74</v>
-      </c>
-      <c r="D144" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C145" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="D145" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C146" t="s">
-        <v>76</v>
-      </c>
-      <c r="D146" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B147" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C147" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D147" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C148" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="D148" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C149" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="D149" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B150" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C150" t="s">
-        <v>80</v>
+        <v>77</v>
+      </c>
+      <c r="D150" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C151" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="D151" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B152" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C152" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="D152" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C153" t="s">
-        <v>73</v>
+        <v>80</v>
+      </c>
+      <c r="D153" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B154" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C154" t="s">
-        <v>74</v>
+        <v>81</v>
+      </c>
+      <c r="D154" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B155" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C155" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B156" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C156" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B157" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C157" t="s">
-        <v>77</v>
+        <v>73</v>
+      </c>
+      <c r="D157" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B158" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C158" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="D158" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B159" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C159" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B160" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C160" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B161" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C161" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="D161" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B162" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C162" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B163" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C163" t="s">
-        <v>73</v>
+        <v>79</v>
+      </c>
+      <c r="D163" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B164" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C164" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B165" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C165" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B166" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C166" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B167" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C167" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B168" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C168" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B169" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C169" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B170" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C170" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B171" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C171" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B172" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C172" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B173" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C173" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B174" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C174" t="s">
-        <v>74</v>
-      </c>
-      <c r="D174" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B175" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C175" t="s">
-        <v>75</v>
-      </c>
-      <c r="D175" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B176" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C176" t="s">
-        <v>76</v>
-      </c>
-      <c r="D176" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B177" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C177" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B178" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C178" t="s">
-        <v>78</v>
-      </c>
-      <c r="D178" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B179" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C179" t="s">
-        <v>79</v>
-      </c>
-      <c r="D179" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B180" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C180" t="s">
-        <v>80</v>
-      </c>
-      <c r="D180" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B181" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C181" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B182" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C182" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B183" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C183" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B184" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C184" t="s">
-        <v>74</v>
-      </c>
-      <c r="D184" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B185" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C185" t="s">
-        <v>75</v>
-      </c>
-      <c r="D185" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B186" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C186" t="s">
-        <v>76</v>
-      </c>
-      <c r="D186" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B187" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C187" t="s">
-        <v>77</v>
-      </c>
-      <c r="D187" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B188" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C188" t="s">
-        <v>78</v>
-      </c>
-      <c r="D188" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B189" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C189" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D189" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B190" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C190" t="s">
-        <v>80</v>
-      </c>
-      <c r="D190" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B191" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C191" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="D191" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B192" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C192" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D192" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B193" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C193" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="D193" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B194" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C194" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D194" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B195" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C195" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D195" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B196" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C196" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D196" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B197" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C197" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D197" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B198" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C198" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D198" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B199" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B200" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C200" t="s">
-        <v>80</v>
+        <v>72</v>
+      </c>
+      <c r="D200" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B201" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C201" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B202" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C202" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B203" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C203" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B204" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C204" t="s">
-        <v>74</v>
-      </c>
-      <c r="D204" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B205" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C205" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D205" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B206" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C206" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D206" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B207" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C207" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D207" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B208" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C208" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D208" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B209" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C209" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D209" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B210" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C210" t="s">
-        <v>80</v>
-      </c>
-      <c r="D210" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B211" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C211" t="s">
-        <v>81</v>
+        <v>72</v>
+      </c>
+      <c r="D211" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B212" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C212" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B213" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C213" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="D213" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B214" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C214" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="D214" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B215" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C215" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D215" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B216" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C216" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D216" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B217" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C217" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D217" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B218" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C218" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D218" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B219" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C219" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D219" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B220" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C220" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D220" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B221" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C221" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B222" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C222" t="s">
         <v>72</v>
       </c>
-      <c r="D222" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B223" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C223" t="s">
         <v>73</v>
       </c>
-      <c r="D223" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B224" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C224" t="s">
         <v>74</v>
       </c>
-      <c r="D224" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B225" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C225" t="s">
         <v>75</v>
       </c>
-      <c r="D225" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B226" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C226" t="s">
         <v>76</v>
       </c>
-      <c r="D226" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B227" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C227" t="s">
         <v>77</v>
       </c>
-      <c r="D227" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B228" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C228" t="s">
         <v>78</v>
       </c>
-      <c r="D228" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B229" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C229" t="s">
         <v>79</v>
       </c>
-      <c r="D229" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B230" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C230" t="s">
         <v>80</v>
       </c>
-      <c r="D230" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B231" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C231" t="s">
         <v>81</v>
@@ -3769,111 +3745,102 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B232" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C232" t="s">
-        <v>72</v>
-      </c>
-      <c r="D232" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B233" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C233" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D233" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B234" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C234" t="s">
-        <v>74</v>
-      </c>
-      <c r="D234" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B235" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C235" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D235" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B236" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C236" t="s">
-        <v>76</v>
-      </c>
-      <c r="D236" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B237" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C237" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D237" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B238" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C238" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D238" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B239" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C239" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D239" t="s">
         <v>100</v>
@@ -3881,136 +3848,136 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B240" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C240" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D240" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B241" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C241" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="D241" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B242" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C242" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D242" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B243" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C243" t="s">
-        <v>73</v>
-      </c>
-      <c r="D243" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B244" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C244" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D244" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B245" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C245" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D245" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B246" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C246" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D246" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B247" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C247" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D247" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B248" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C248" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D248" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B249" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C249" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D249" t="s">
         <v>83</v>
@@ -4018,676 +3985,700 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B250" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C250" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D250" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B251" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C251" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="D251" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B252" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C252" t="s">
-        <v>73</v>
+        <v>80</v>
+      </c>
+      <c r="D252" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B253" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C253" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D253" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B254" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C254" t="s">
-        <v>75</v>
-      </c>
-      <c r="D254" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B255" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C255" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D255" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B256" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C256" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="D256" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B257" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C257" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="D257" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B258" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C258" t="s">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="D258" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B259" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C259" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="D259" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B260" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C260" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D260" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B261" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C261" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D261" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B262" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C262" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D262" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B263" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C263" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D263" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B264" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C264" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D264" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B265" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C265" t="s">
-        <v>79</v>
-      </c>
-      <c r="D265" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B266" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C266" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D266" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B267" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C267" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D267" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B268" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C268" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D268" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B269" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C269" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D269" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B270" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C270" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D270" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B271" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C271" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D271" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B272" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C272" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D272" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B273" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C273" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D273" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B274" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C274" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D274" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B275" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C275" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D275" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B276" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C276" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B277" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C277" t="s">
-        <v>81</v>
+        <v>73</v>
+      </c>
+      <c r="D277" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B278" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C278" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="D278" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B279" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C279" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="D279" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B280" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C280" t="s">
-        <v>74</v>
-      </c>
-      <c r="D280" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B281" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C281" t="s">
-        <v>75</v>
-      </c>
-      <c r="D281" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B282" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C282" t="s">
-        <v>76</v>
-      </c>
-      <c r="D282" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B283" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C283" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D283" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B284" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C284" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B285" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C285" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D285" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B286" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C286" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D286" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B287" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C287" t="s">
-        <v>81</v>
+        <v>76</v>
+      </c>
+      <c r="D287" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B288" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C288" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D288" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B289" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C289" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D289" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B290" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C290" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D290" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B291" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C291" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B292" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C292" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D292" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B293" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C293" t="s">
-        <v>77</v>
-      </c>
-      <c r="D293" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B294" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C294" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D294" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B295" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C295" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D295" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B296" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C296" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D296" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B297" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C297" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="D297" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B298" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C298" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="D298" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B299" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C299" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="D299" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B300" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C300" t="s">
         <v>78</v>
       </c>
+      <c r="D300" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B301" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C301" t="s">
         <v>79</v>
@@ -4695,398 +4686,807 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B302" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C302" t="s">
-        <v>72</v>
-      </c>
-      <c r="D302" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B303" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C303" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B304" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C304" t="s">
-        <v>74</v>
-      </c>
-      <c r="D304" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B305" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C305" t="s">
-        <v>75</v>
-      </c>
-      <c r="D305" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B306" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C306" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D306" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B307" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C307" t="s">
-        <v>77</v>
-      </c>
-      <c r="D307" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B308" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C308" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D308" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B309" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C309" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D309" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B310" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C310" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D310" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B311" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C311" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="D311" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B312" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C312" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="D312" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B313" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C313" t="s">
-        <v>73</v>
+        <v>80</v>
+      </c>
+      <c r="D313" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B314" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C314" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D314" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B315" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C315" t="s">
-        <v>75</v>
-      </c>
-      <c r="D315" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B316" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C316" t="s">
-        <v>76</v>
-      </c>
-      <c r="D316" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B317" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C317" t="s">
-        <v>77</v>
-      </c>
-      <c r="D317" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B318" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C318" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D318" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B319" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C319" t="s">
-        <v>79</v>
-      </c>
-      <c r="D319" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B320" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C320" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D320" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B321" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C321" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B322" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C322" t="s">
-        <v>72</v>
-      </c>
-      <c r="D322" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B323" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C323" t="s">
-        <v>73</v>
+        <v>79</v>
+      </c>
+      <c r="D323" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B324" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C324" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D324" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B325" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C325" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D325" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B326" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C326" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B327" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C327" t="s">
-        <v>77</v>
-      </c>
-      <c r="D327" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B328" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C328" t="s">
-        <v>78</v>
-      </c>
-      <c r="D328" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B329" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C329" t="s">
-        <v>79</v>
-      </c>
-      <c r="D329" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B330" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C330" t="s">
-        <v>80</v>
-      </c>
-      <c r="D330" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
+        <v>35</v>
+      </c>
+      <c r="B331" t="s">
+        <v>69</v>
+      </c>
+      <c r="C331" t="s">
+        <v>72</v>
+      </c>
+      <c r="D331" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" t="s">
+        <v>35</v>
+      </c>
+      <c r="B332" t="s">
+        <v>69</v>
+      </c>
+      <c r="C332" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" t="s">
+        <v>35</v>
+      </c>
+      <c r="B333" t="s">
+        <v>69</v>
+      </c>
+      <c r="C333" t="s">
+        <v>74</v>
+      </c>
+      <c r="D333" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" t="s">
+        <v>35</v>
+      </c>
+      <c r="B334" t="s">
+        <v>69</v>
+      </c>
+      <c r="C334" t="s">
+        <v>75</v>
+      </c>
+      <c r="D334" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" t="s">
+        <v>35</v>
+      </c>
+      <c r="B335" t="s">
+        <v>69</v>
+      </c>
+      <c r="C335" t="s">
+        <v>76</v>
+      </c>
+      <c r="D335" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" t="s">
+        <v>35</v>
+      </c>
+      <c r="B336" t="s">
+        <v>69</v>
+      </c>
+      <c r="C336" t="s">
+        <v>77</v>
+      </c>
+      <c r="D336" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" t="s">
+        <v>35</v>
+      </c>
+      <c r="B337" t="s">
+        <v>69</v>
+      </c>
+      <c r="C337" t="s">
+        <v>78</v>
+      </c>
+      <c r="D337" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" t="s">
+        <v>35</v>
+      </c>
+      <c r="B338" t="s">
+        <v>69</v>
+      </c>
+      <c r="C338" t="s">
+        <v>79</v>
+      </c>
+      <c r="D338" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" t="s">
+        <v>35</v>
+      </c>
+      <c r="B339" t="s">
+        <v>69</v>
+      </c>
+      <c r="C339" t="s">
+        <v>80</v>
+      </c>
+      <c r="D339" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" t="s">
+        <v>35</v>
+      </c>
+      <c r="B340" t="s">
+        <v>69</v>
+      </c>
+      <c r="C340" t="s">
+        <v>81</v>
+      </c>
+      <c r="D340" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" t="s">
+        <v>35</v>
+      </c>
+      <c r="B341" t="s">
+        <v>69</v>
+      </c>
+      <c r="C341" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" t="s">
+        <v>36</v>
+      </c>
+      <c r="B342" t="s">
+        <v>70</v>
+      </c>
+      <c r="C342" t="s">
+        <v>72</v>
+      </c>
+      <c r="D342" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" t="s">
+        <v>36</v>
+      </c>
+      <c r="B343" t="s">
+        <v>70</v>
+      </c>
+      <c r="C343" t="s">
+        <v>73</v>
+      </c>
+      <c r="D343" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" t="s">
+        <v>36</v>
+      </c>
+      <c r="B344" t="s">
+        <v>70</v>
+      </c>
+      <c r="C344" t="s">
+        <v>74</v>
+      </c>
+      <c r="D344" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" t="s">
+        <v>36</v>
+      </c>
+      <c r="B345" t="s">
+        <v>70</v>
+      </c>
+      <c r="C345" t="s">
+        <v>75</v>
+      </c>
+      <c r="D345" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" t="s">
+        <v>36</v>
+      </c>
+      <c r="B346" t="s">
+        <v>70</v>
+      </c>
+      <c r="C346" t="s">
+        <v>76</v>
+      </c>
+      <c r="D346" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" t="s">
+        <v>36</v>
+      </c>
+      <c r="B347" t="s">
+        <v>70</v>
+      </c>
+      <c r="C347" t="s">
+        <v>77</v>
+      </c>
+      <c r="D347" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" t="s">
+        <v>36</v>
+      </c>
+      <c r="B348" t="s">
+        <v>70</v>
+      </c>
+      <c r="C348" t="s">
+        <v>78</v>
+      </c>
+      <c r="D348" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" t="s">
+        <v>36</v>
+      </c>
+      <c r="B349" t="s">
+        <v>70</v>
+      </c>
+      <c r="C349" t="s">
+        <v>79</v>
+      </c>
+      <c r="D349" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" t="s">
+        <v>36</v>
+      </c>
+      <c r="B350" t="s">
+        <v>70</v>
+      </c>
+      <c r="C350" t="s">
+        <v>80</v>
+      </c>
+      <c r="D350" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" t="s">
+        <v>36</v>
+      </c>
+      <c r="B351" t="s">
+        <v>70</v>
+      </c>
+      <c r="C351" t="s">
+        <v>81</v>
+      </c>
+      <c r="D351" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" t="s">
+        <v>36</v>
+      </c>
+      <c r="B352" t="s">
+        <v>70</v>
+      </c>
+      <c r="C352" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" t="s">
         <v>37</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B353" t="s">
         <v>71</v>
       </c>
-      <c r="C331" t="s">
+      <c r="C353" t="s">
+        <v>72</v>
+      </c>
+      <c r="D353" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" t="s">
+        <v>37</v>
+      </c>
+      <c r="B354" t="s">
+        <v>71</v>
+      </c>
+      <c r="C354" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" t="s">
+        <v>37</v>
+      </c>
+      <c r="B355" t="s">
+        <v>71</v>
+      </c>
+      <c r="C355" t="s">
+        <v>74</v>
+      </c>
+      <c r="D355" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" t="s">
+        <v>37</v>
+      </c>
+      <c r="B356" t="s">
+        <v>71</v>
+      </c>
+      <c r="C356" t="s">
+        <v>75</v>
+      </c>
+      <c r="D356" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" t="s">
+        <v>37</v>
+      </c>
+      <c r="B357" t="s">
+        <v>71</v>
+      </c>
+      <c r="C357" t="s">
+        <v>76</v>
+      </c>
+      <c r="D357" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" t="s">
+        <v>37</v>
+      </c>
+      <c r="B358" t="s">
+        <v>71</v>
+      </c>
+      <c r="C358" t="s">
+        <v>77</v>
+      </c>
+      <c r="D358" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" t="s">
+        <v>37</v>
+      </c>
+      <c r="B359" t="s">
+        <v>71</v>
+      </c>
+      <c r="C359" t="s">
+        <v>78</v>
+      </c>
+      <c r="D359" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" t="s">
+        <v>37</v>
+      </c>
+      <c r="B360" t="s">
+        <v>71</v>
+      </c>
+      <c r="C360" t="s">
+        <v>79</v>
+      </c>
+      <c r="D360" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" t="s">
+        <v>37</v>
+      </c>
+      <c r="B361" t="s">
+        <v>71</v>
+      </c>
+      <c r="C361" t="s">
+        <v>80</v>
+      </c>
+      <c r="D361" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" t="s">
+        <v>37</v>
+      </c>
+      <c r="B362" t="s">
+        <v>71</v>
+      </c>
+      <c r="C362" t="s">
         <v>81</v>
+      </c>
+      <c r="D362" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" t="s">
+        <v>37</v>
+      </c>
+      <c r="B363" t="s">
+        <v>71</v>
+      </c>
+      <c r="C363" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/control_acceso/accesos_limpios_docentes.xlsx
+++ b/control_acceso/accesos_limpios_docentes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="138">
   <si>
     <t>nombre</t>
   </si>
@@ -232,172 +232,202 @@
     <t>1152701729</t>
   </si>
   <si>
-    <t>viernes , 15 de mayo</t>
-  </si>
-  <si>
-    <t>lunes , 18 de mayo</t>
-  </si>
-  <si>
-    <t>martes , 19 de mayo</t>
-  </si>
-  <si>
-    <t>miércoles , 20 de mayo</t>
-  </si>
-  <si>
-    <t>jueves , 21 de mayo</t>
-  </si>
-  <si>
-    <t>viernes , 22 de mayo</t>
-  </si>
-  <si>
-    <t>lunes , 25 de mayo</t>
-  </si>
-  <si>
-    <t>martes , 26 de mayo</t>
-  </si>
-  <si>
-    <t>miércoles , 27 de mayo</t>
-  </si>
-  <si>
-    <t>jueves , 28 de mayo</t>
-  </si>
-  <si>
-    <t>viernes , 29 de mayo</t>
+    <t>martes , 30 de junio</t>
+  </si>
+  <si>
+    <t>miércoles , 01 de julio</t>
+  </si>
+  <si>
+    <t>jueves , 02 de julio</t>
+  </si>
+  <si>
+    <t>viernes , 03 de julio</t>
+  </si>
+  <si>
+    <t>lunes , 06 de julio</t>
+  </si>
+  <si>
+    <t>martes , 07 de julio</t>
+  </si>
+  <si>
+    <t>miércoles , 08 de julio</t>
+  </si>
+  <si>
+    <t>jueves , 09 de julio</t>
+  </si>
+  <si>
+    <t>viernes , 10 de julio</t>
+  </si>
+  <si>
+    <t>lunes , 13 de julio</t>
+  </si>
+  <si>
+    <t>martes , 14 de julio</t>
+  </si>
+  <si>
+    <t>miércoles , 15 de julio</t>
+  </si>
+  <si>
+    <t>jueves , 16 de julio</t>
+  </si>
+  <si>
+    <t>06:17</t>
   </si>
   <si>
     <t>06:16</t>
   </si>
   <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>06:18</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
     <t>06:11</t>
   </si>
   <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>14:38</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>06:14</t>
-  </si>
-  <si>
-    <t>06:21</t>
+    <t>06:06</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>15:33</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>06:12</t>
   </si>
   <si>
     <t>06:28</t>
   </si>
   <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>06:12</t>
-  </si>
-  <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>06:36</t>
-  </si>
-  <si>
-    <t>06:35</t>
+    <t>06:34</t>
   </si>
   <si>
     <t>06:22</t>
   </si>
   <si>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
     <t>06:30</t>
   </si>
   <si>
-    <t>06:31</t>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>10:33</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>07:04</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>06:29</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>06:52</t>
+  </si>
+  <si>
+    <t>06:38</t>
   </si>
   <si>
     <t>06:42</t>
   </si>
   <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>06:37</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>08:38</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>08:16</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>15:51</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>15:47</t>
-  </si>
-  <si>
-    <t>13:39</t>
-  </si>
-  <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>06:33</t>
-  </si>
-  <si>
-    <t>06:29</t>
-  </si>
-  <si>
-    <t>06:07</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:22</t>
-  </si>
-  <si>
-    <t>15:41</t>
-  </si>
-  <si>
-    <t>06:43</t>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>14:45</t>
   </si>
 </sst>
 </file>
@@ -755,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D363"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -783,7 +813,7 @@
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -796,6 +826,9 @@
       <c r="C3" t="s">
         <v>73</v>
       </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
@@ -807,9 +840,6 @@
       <c r="C4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
@@ -822,7 +852,7 @@
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -835,9 +865,6 @@
       <c r="C6" t="s">
         <v>76</v>
       </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
@@ -850,7 +877,7 @@
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -863,6 +890,9 @@
       <c r="C8" t="s">
         <v>78</v>
       </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
@@ -875,7 +905,7 @@
         <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -889,7 +919,7 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -902,9 +932,6 @@
       <c r="C11" t="s">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
@@ -916,30 +943,36 @@
       <c r="C12" t="s">
         <v>82</v>
       </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -950,10 +983,10 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -964,7 +997,10 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -975,7 +1011,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
         <v>91</v>
@@ -989,10 +1025,10 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1003,10 +1039,10 @@
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1017,10 +1053,10 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1031,10 +1067,10 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1045,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1059,57 +1095,63 @@
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>80</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>82</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1120,10 +1162,10 @@
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1134,10 +1176,10 @@
         <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1148,10 +1190,10 @@
         <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1162,10 +1204,10 @@
         <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1176,10 +1218,10 @@
         <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1190,7 +1232,10 @@
         <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="D33" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1201,91 +1246,91 @@
         <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="D34" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1296,10 +1341,7 @@
         <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1310,10 +1352,10 @@
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1324,10 +1366,10 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1338,10 +1380,10 @@
         <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1352,113 +1394,119 @@
         <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="D45" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>77</v>
+      </c>
+      <c r="D46" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>73</v>
+        <v>78</v>
+      </c>
+      <c r="D47" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
-      </c>
-      <c r="D50" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1469,10 +1517,10 @@
         <v>42</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1483,10 +1531,10 @@
         <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1497,32 +1545,35 @@
         <v>42</v>
       </c>
       <c r="C56" t="s">
-        <v>82</v>
+        <v>74</v>
+      </c>
+      <c r="D56" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C57" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D58" t="s">
         <v>93</v>
@@ -1530,99 +1581,111 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D59" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C60" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D60" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D61" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C62" t="s">
-        <v>77</v>
+        <v>80</v>
+      </c>
+      <c r="D62" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>82</v>
+      </c>
+      <c r="D64" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C65" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="D65" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="D66" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1633,532 +1696,538 @@
         <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="D69" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="D70" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D71" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C72" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C73" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D73" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D74" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
-      </c>
-      <c r="D76" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C78" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C79" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C80" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="D80" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D81" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D82" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D83" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D84" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>78</v>
-      </c>
-      <c r="D85" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D87" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D88" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C89" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="D89" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C90" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D90" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C91" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D91" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C92" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D92" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C93" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D93" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C94" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C95" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D95" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C96" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D96" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C97" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D97" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C98" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D98" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C99" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C100" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C101" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D101" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C102" t="s">
-        <v>73</v>
-      </c>
-      <c r="D102" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C103" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+      <c r="D103" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C104" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D104" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C105" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D105" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C106" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D106" t="s">
         <v>93</v>
@@ -2166,697 +2235,712 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C107" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D107" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C108" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D108" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C109" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D109" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C110" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D110" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C111" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="D111" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C112" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D112" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C113" t="s">
-        <v>73</v>
+        <v>79</v>
+      </c>
+      <c r="D113" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D114" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C115" t="s">
-        <v>75</v>
-      </c>
-      <c r="D115" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C116" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D116" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C117" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D117" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C118" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D118" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C119" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D119" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C120" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D120" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C121" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D121" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C122" t="s">
-        <v>82</v>
+        <v>75</v>
+      </c>
+      <c r="D122" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C123" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D123" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C124" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D124" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C125" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D125" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C126" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D126" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C127" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D127" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C128" t="s">
-        <v>77</v>
-      </c>
-      <c r="D128" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C129" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D129" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C130" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D130" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C131" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D131" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C132" t="s">
-        <v>81</v>
+        <v>72</v>
+      </c>
+      <c r="D132" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C133" t="s">
-        <v>82</v>
+        <v>73</v>
+      </c>
+      <c r="D133" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B134" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C134" t="s">
-        <v>72</v>
-      </c>
-      <c r="D134" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B135" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C135" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="D135" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B136" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C136" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D136" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B137" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C137" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D137" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B138" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C138" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D138" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B139" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C139" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D139" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B140" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C140" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D140" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C141" t="s">
-        <v>79</v>
-      </c>
-      <c r="D141" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D142" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C143" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D143" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C144" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="D144" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C145" t="s">
         <v>72</v>
       </c>
-      <c r="D145" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C146" t="s">
         <v>73</v>
       </c>
+      <c r="D146" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C147" t="s">
         <v>74</v>
       </c>
       <c r="D147" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C148" t="s">
         <v>75</v>
       </c>
       <c r="D148" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C149" t="s">
         <v>76</v>
       </c>
       <c r="D149" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C150" t="s">
         <v>77</v>
       </c>
       <c r="D150" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C151" t="s">
         <v>78</v>
       </c>
       <c r="D151" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C152" t="s">
         <v>79</v>
       </c>
       <c r="D152" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C153" t="s">
         <v>80</v>
       </c>
       <c r="D153" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C154" t="s">
         <v>81</v>
       </c>
       <c r="D154" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C155" t="s">
         <v>82</v>
       </c>
+      <c r="D155" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C156" t="s">
-        <v>72</v>
+        <v>83</v>
+      </c>
+      <c r="D156" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C157" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D157" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C158" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D158" t="s">
         <v>117</v>
@@ -2864,583 +2948,646 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C159" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="D159" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C160" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="D160" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C161" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D161" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C162" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="D162" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C163" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D163" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C164" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="D164" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C165" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="D165" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C166" t="s">
-        <v>82</v>
+        <v>80</v>
+      </c>
+      <c r="D166" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C167" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C168" t="s">
-        <v>73</v>
+        <v>82</v>
+      </c>
+      <c r="D168" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C169" t="s">
-        <v>74</v>
+        <v>83</v>
+      </c>
+      <c r="D169" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C170" t="s">
-        <v>75</v>
+        <v>84</v>
+      </c>
+      <c r="D170" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C171" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="D171" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C172" t="s">
-        <v>77</v>
+        <v>73</v>
+      </c>
+      <c r="D172" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C173" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="D173" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C174" t="s">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="D174" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C175" t="s">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="D175" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C176" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="D176" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C177" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="D177" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C178" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="D178" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C179" t="s">
-        <v>73</v>
+        <v>80</v>
+      </c>
+      <c r="D179" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C180" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C181" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="D181" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C182" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C183" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B184" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C184" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B185" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C185" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="D185" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B186" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C186" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B187" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C187" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="D187" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B188" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C188" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B189" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C189" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D189" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B190" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C190" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B191" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C191" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D191" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B192" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C192" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D192" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B193" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C193" t="s">
-        <v>76</v>
-      </c>
-      <c r="D193" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B194" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C194" t="s">
-        <v>77</v>
-      </c>
-      <c r="D194" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B195" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C195" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D195" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B196" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C196" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D196" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B197" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C197" t="s">
-        <v>80</v>
-      </c>
-      <c r="D197" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B198" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C198" t="s">
-        <v>81</v>
-      </c>
-      <c r="D198" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B199" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C199" t="s">
-        <v>82</v>
+        <v>74</v>
+      </c>
+      <c r="D199" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B200" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C200" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D200" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B201" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C201" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="D201" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B202" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C202" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="D202" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B203" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C203" t="s">
-        <v>75</v>
+        <v>78</v>
+      </c>
+      <c r="D203" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B204" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C204" t="s">
-        <v>76</v>
+        <v>79</v>
+      </c>
+      <c r="D204" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B205" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C205" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D205" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B206" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C206" t="s">
-        <v>78</v>
-      </c>
-      <c r="D206" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B207" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C207" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D207" t="s">
         <v>89</v>
@@ -3448,1212 +3595,1239 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B208" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C208" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D208" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B209" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C209" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D209" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C210" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C211" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D211" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C212" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B213" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C213" t="s">
-        <v>74</v>
-      </c>
-      <c r="D213" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B214" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C214" t="s">
-        <v>75</v>
-      </c>
-      <c r="D214" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B215" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C215" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D215" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C216" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D216" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B217" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C217" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D217" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B218" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C218" t="s">
-        <v>79</v>
-      </c>
-      <c r="D218" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B219" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C219" t="s">
-        <v>80</v>
-      </c>
-      <c r="D219" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C220" t="s">
-        <v>81</v>
-      </c>
-      <c r="D220" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B221" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C221" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C222" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B223" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C223" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="D223" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B224" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C224" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="D224" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B225" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C225" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="D225" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B226" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C226" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="D226" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B227" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C227" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="D227" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B228" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C228" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="D228" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B229" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C229" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="D229" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B230" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C230" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="D230" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B231" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C231" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="D231" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B232" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C232" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B233" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C233" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D233" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B234" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C234" t="s">
-        <v>73</v>
+        <v>83</v>
+      </c>
+      <c r="D234" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B235" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C235" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D235" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B236" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C236" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="D236" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B237" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C237" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D237" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B238" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C238" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D238" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B239" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C239" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D239" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B240" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C240" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D240" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B241" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C241" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D241" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B242" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C242" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D242" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B243" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C243" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="D243" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B244" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C244" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D244" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B245" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C245" t="s">
-        <v>73</v>
-      </c>
-      <c r="D245" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B246" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C246" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D246" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B247" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C247" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D247" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B248" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C248" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D248" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B249" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C249" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D249" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B250" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C250" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D250" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B251" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C251" t="s">
-        <v>79</v>
-      </c>
-      <c r="D251" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B252" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C252" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D252" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B253" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C253" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D253" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B254" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C254" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="D254" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B255" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C255" t="s">
-        <v>72</v>
-      </c>
-      <c r="D255" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B256" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C256" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D256" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B257" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C257" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D257" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B258" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C258" t="s">
-        <v>75</v>
-      </c>
-      <c r="D258" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B259" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C259" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D259" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B260" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C260" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D260" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B261" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C261" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D261" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B262" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C262" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D262" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B263" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C263" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D263" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B264" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C264" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D264" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B265" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C265" t="s">
-        <v>82</v>
+        <v>75</v>
+      </c>
+      <c r="D265" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B266" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C266" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D266" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B267" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C267" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D267" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B268" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C268" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D268" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B269" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C269" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D269" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B270" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C270" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D270" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B271" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C271" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D271" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B272" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C272" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D272" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B273" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C273" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D273" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B274" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C274" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D274" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B275" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C275" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D275" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B276" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C276" t="s">
-        <v>82</v>
+        <v>73</v>
+      </c>
+      <c r="D276" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B277" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C277" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D277" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B278" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C278" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D278" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B279" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C279" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D279" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B280" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C280" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="D280" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B281" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C281" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="D281" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B282" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C282" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="D282" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B283" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C283" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B284" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C284" t="s">
-        <v>73</v>
+        <v>81</v>
+      </c>
+      <c r="D284" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B285" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C285" t="s">
-        <v>74</v>
-      </c>
-      <c r="D285" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B286" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C286" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D286" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B287" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C287" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D287" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B288" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C288" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D288" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B289" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C289" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D289" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B290" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C290" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D290" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B291" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C291" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D291" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B292" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C292" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D292" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B293" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C293" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="D293" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B294" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C294" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D294" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B295" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C295" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D295" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B296" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C296" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D296" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B297" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C297" t="s">
-        <v>75</v>
-      </c>
-      <c r="D297" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B298" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C298" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D298" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B299" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C299" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D299" t="s">
         <v>93</v>
@@ -4661,396 +4835,441 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B300" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C300" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D300" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B301" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C301" t="s">
-        <v>79</v>
+        <v>72</v>
+      </c>
+      <c r="D301" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B302" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C302" t="s">
-        <v>80</v>
+        <v>73</v>
+      </c>
+      <c r="D302" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B303" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C303" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="D303" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B304" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C304" t="s">
-        <v>82</v>
+        <v>75</v>
+      </c>
+      <c r="D304" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B305" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C305" t="s">
-        <v>72</v>
+        <v>76</v>
+      </c>
+      <c r="D305" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B306" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C306" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D306" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B307" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C307" t="s">
-        <v>74</v>
+        <v>78</v>
+      </c>
+      <c r="D307" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B308" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C308" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D308" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B309" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C309" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D309" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B310" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C310" t="s">
-        <v>77</v>
-      </c>
-      <c r="D310" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B311" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C311" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D311" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B312" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C312" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D312" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B313" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C313" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D313" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B314" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C314" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D314" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B315" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C315" t="s">
-        <v>82</v>
+        <v>73</v>
+      </c>
+      <c r="D315" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B316" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C316" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="D316" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B317" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C317" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="D317" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B318" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C318" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D318" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B319" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C319" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="D319" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B320" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C320" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D320" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B321" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C321" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="D321" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B322" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C322" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="D322" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B323" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C323" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D323" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B324" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C324" t="s">
-        <v>80</v>
-      </c>
-      <c r="D324" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B325" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C325" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D325" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B326" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C326" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="D326" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B327" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C327" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="D327" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B328" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C328" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="D328" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B329" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C329" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="D329" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B330" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C330" t="s">
-        <v>79</v>
+        <v>77</v>
+      </c>
+      <c r="D330" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B331" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C331" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D331" t="s">
         <v>112</v>
@@ -5058,435 +5277,1262 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B332" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C332" t="s">
-        <v>73</v>
+        <v>81</v>
+      </c>
+      <c r="D332" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B333" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C333" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D333" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B334" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C334" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D334" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B335" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C335" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D335" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B336" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C336" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D336" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B337" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C337" t="s">
-        <v>78</v>
-      </c>
-      <c r="D337" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B338" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C338" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D338" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B339" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C339" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D339" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B340" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C340" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D340" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B341" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C341" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="D341" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B342" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C342" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D342" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B343" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C343" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B344" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C344" t="s">
-        <v>74</v>
-      </c>
-      <c r="D344" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B345" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C345" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D345" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B346" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C346" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D346" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B347" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C347" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D347" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B348" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C348" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D348" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B349" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C349" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D349" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B350" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C350" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D350" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B351" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C351" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D351" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B352" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C352" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B353" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C353" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D353" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B354" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C354" t="s">
-        <v>73</v>
+        <v>78</v>
+      </c>
+      <c r="D354" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B355" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C355" t="s">
-        <v>74</v>
-      </c>
-      <c r="D355" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B356" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C356" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D356" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B357" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C357" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D357" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B358" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C358" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D358" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B359" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C359" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D359" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B360" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C360" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D360" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B361" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C361" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D361" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B362" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C362" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D362" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
+        <v>32</v>
+      </c>
+      <c r="B363" t="s">
+        <v>66</v>
+      </c>
+      <c r="C363" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" t="s">
+        <v>32</v>
+      </c>
+      <c r="B364" t="s">
+        <v>66</v>
+      </c>
+      <c r="C364" t="s">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" t="s">
+        <v>32</v>
+      </c>
+      <c r="B365" t="s">
+        <v>66</v>
+      </c>
+      <c r="C365" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" t="s">
+        <v>32</v>
+      </c>
+      <c r="B366" t="s">
+        <v>66</v>
+      </c>
+      <c r="C366" t="s">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" t="s">
+        <v>32</v>
+      </c>
+      <c r="B367" t="s">
+        <v>66</v>
+      </c>
+      <c r="C367" t="s">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" t="s">
+        <v>32</v>
+      </c>
+      <c r="B368" t="s">
+        <v>66</v>
+      </c>
+      <c r="C368" t="s">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" t="s">
+        <v>32</v>
+      </c>
+      <c r="B369" t="s">
+        <v>66</v>
+      </c>
+      <c r="C369" t="s">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" t="s">
+        <v>32</v>
+      </c>
+      <c r="B370" t="s">
+        <v>66</v>
+      </c>
+      <c r="C370" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" t="s">
+        <v>32</v>
+      </c>
+      <c r="B371" t="s">
+        <v>66</v>
+      </c>
+      <c r="C371" t="s">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" t="s">
+        <v>32</v>
+      </c>
+      <c r="B372" t="s">
+        <v>66</v>
+      </c>
+      <c r="C372" t="s">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" t="s">
+        <v>32</v>
+      </c>
+      <c r="B373" t="s">
+        <v>66</v>
+      </c>
+      <c r="C373" t="s">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" t="s">
+        <v>33</v>
+      </c>
+      <c r="B374" t="s">
+        <v>67</v>
+      </c>
+      <c r="C374" t="s">
+        <v>72</v>
+      </c>
+      <c r="D374" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" t="s">
+        <v>33</v>
+      </c>
+      <c r="B375" t="s">
+        <v>67</v>
+      </c>
+      <c r="C375" t="s">
+        <v>73</v>
+      </c>
+      <c r="D375" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" t="s">
+        <v>33</v>
+      </c>
+      <c r="B376" t="s">
+        <v>67</v>
+      </c>
+      <c r="C376" t="s">
+        <v>74</v>
+      </c>
+      <c r="D376" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" t="s">
+        <v>33</v>
+      </c>
+      <c r="B377" t="s">
+        <v>67</v>
+      </c>
+      <c r="C377" t="s">
+        <v>75</v>
+      </c>
+      <c r="D377" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" t="s">
+        <v>33</v>
+      </c>
+      <c r="B378" t="s">
+        <v>67</v>
+      </c>
+      <c r="C378" t="s">
+        <v>76</v>
+      </c>
+      <c r="D378" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" t="s">
+        <v>33</v>
+      </c>
+      <c r="B379" t="s">
+        <v>67</v>
+      </c>
+      <c r="C379" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" t="s">
+        <v>33</v>
+      </c>
+      <c r="B380" t="s">
+        <v>67</v>
+      </c>
+      <c r="C380" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" t="s">
+        <v>33</v>
+      </c>
+      <c r="B381" t="s">
+        <v>67</v>
+      </c>
+      <c r="C381" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" t="s">
+        <v>33</v>
+      </c>
+      <c r="B382" t="s">
+        <v>67</v>
+      </c>
+      <c r="C382" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" t="s">
+        <v>33</v>
+      </c>
+      <c r="B383" t="s">
+        <v>67</v>
+      </c>
+      <c r="C383" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" t="s">
+        <v>33</v>
+      </c>
+      <c r="B384" t="s">
+        <v>67</v>
+      </c>
+      <c r="C384" t="s">
+        <v>82</v>
+      </c>
+      <c r="D384" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" t="s">
+        <v>33</v>
+      </c>
+      <c r="B385" t="s">
+        <v>67</v>
+      </c>
+      <c r="C385" t="s">
+        <v>83</v>
+      </c>
+      <c r="D385" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" t="s">
+        <v>33</v>
+      </c>
+      <c r="B386" t="s">
+        <v>67</v>
+      </c>
+      <c r="C386" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" t="s">
+        <v>34</v>
+      </c>
+      <c r="B387" t="s">
+        <v>68</v>
+      </c>
+      <c r="C387" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" t="s">
+        <v>34</v>
+      </c>
+      <c r="B388" t="s">
+        <v>68</v>
+      </c>
+      <c r="C388" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" t="s">
+        <v>34</v>
+      </c>
+      <c r="B389" t="s">
+        <v>68</v>
+      </c>
+      <c r="C389" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" t="s">
+        <v>34</v>
+      </c>
+      <c r="B390" t="s">
+        <v>68</v>
+      </c>
+      <c r="C390" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" t="s">
+        <v>34</v>
+      </c>
+      <c r="B391" t="s">
+        <v>68</v>
+      </c>
+      <c r="C391" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" t="s">
+        <v>35</v>
+      </c>
+      <c r="B392" t="s">
+        <v>69</v>
+      </c>
+      <c r="C392" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" t="s">
+        <v>35</v>
+      </c>
+      <c r="B393" t="s">
+        <v>69</v>
+      </c>
+      <c r="C393" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" t="s">
+        <v>35</v>
+      </c>
+      <c r="B394" t="s">
+        <v>69</v>
+      </c>
+      <c r="C394" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" t="s">
+        <v>35</v>
+      </c>
+      <c r="B395" t="s">
+        <v>69</v>
+      </c>
+      <c r="C395" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" t="s">
+        <v>35</v>
+      </c>
+      <c r="B396" t="s">
+        <v>69</v>
+      </c>
+      <c r="C396" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" t="s">
+        <v>35</v>
+      </c>
+      <c r="B397" t="s">
+        <v>69</v>
+      </c>
+      <c r="C397" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" t="s">
+        <v>35</v>
+      </c>
+      <c r="B398" t="s">
+        <v>69</v>
+      </c>
+      <c r="C398" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" t="s">
+        <v>35</v>
+      </c>
+      <c r="B399" t="s">
+        <v>69</v>
+      </c>
+      <c r="C399" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" t="s">
+        <v>35</v>
+      </c>
+      <c r="B400" t="s">
+        <v>69</v>
+      </c>
+      <c r="C400" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" t="s">
+        <v>35</v>
+      </c>
+      <c r="B401" t="s">
+        <v>69</v>
+      </c>
+      <c r="C401" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" t="s">
+        <v>35</v>
+      </c>
+      <c r="B402" t="s">
+        <v>69</v>
+      </c>
+      <c r="C402" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" t="s">
+        <v>35</v>
+      </c>
+      <c r="B403" t="s">
+        <v>69</v>
+      </c>
+      <c r="C403" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" t="s">
+        <v>35</v>
+      </c>
+      <c r="B404" t="s">
+        <v>69</v>
+      </c>
+      <c r="C404" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" t="s">
+        <v>36</v>
+      </c>
+      <c r="B405" t="s">
+        <v>70</v>
+      </c>
+      <c r="C405" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" t="s">
+        <v>36</v>
+      </c>
+      <c r="B406" t="s">
+        <v>70</v>
+      </c>
+      <c r="C406" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" t="s">
+        <v>36</v>
+      </c>
+      <c r="B407" t="s">
+        <v>70</v>
+      </c>
+      <c r="C407" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" t="s">
+        <v>36</v>
+      </c>
+      <c r="B408" t="s">
+        <v>70</v>
+      </c>
+      <c r="C408" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" t="s">
+        <v>36</v>
+      </c>
+      <c r="B409" t="s">
+        <v>70</v>
+      </c>
+      <c r="C409" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" t="s">
+        <v>36</v>
+      </c>
+      <c r="B410" t="s">
+        <v>70</v>
+      </c>
+      <c r="C410" t="s">
+        <v>77</v>
+      </c>
+      <c r="D410" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" t="s">
+        <v>36</v>
+      </c>
+      <c r="B411" t="s">
+        <v>70</v>
+      </c>
+      <c r="C411" t="s">
+        <v>78</v>
+      </c>
+      <c r="D411" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" t="s">
+        <v>36</v>
+      </c>
+      <c r="B412" t="s">
+        <v>70</v>
+      </c>
+      <c r="C412" t="s">
+        <v>79</v>
+      </c>
+      <c r="D412" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" t="s">
+        <v>36</v>
+      </c>
+      <c r="B413" t="s">
+        <v>70</v>
+      </c>
+      <c r="C413" t="s">
+        <v>80</v>
+      </c>
+      <c r="D413" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" t="s">
+        <v>36</v>
+      </c>
+      <c r="B414" t="s">
+        <v>70</v>
+      </c>
+      <c r="C414" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" t="s">
+        <v>36</v>
+      </c>
+      <c r="B415" t="s">
+        <v>70</v>
+      </c>
+      <c r="C415" t="s">
+        <v>82</v>
+      </c>
+      <c r="D415" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" t="s">
+        <v>36</v>
+      </c>
+      <c r="B416" t="s">
+        <v>70</v>
+      </c>
+      <c r="C416" t="s">
+        <v>83</v>
+      </c>
+      <c r="D416" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" t="s">
+        <v>36</v>
+      </c>
+      <c r="B417" t="s">
+        <v>70</v>
+      </c>
+      <c r="C417" t="s">
+        <v>84</v>
+      </c>
+      <c r="D417" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" t="s">
         <v>37</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B418" t="s">
         <v>71</v>
       </c>
-      <c r="C363" t="s">
+      <c r="C418" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" t="s">
+        <v>37</v>
+      </c>
+      <c r="B419" t="s">
+        <v>71</v>
+      </c>
+      <c r="C419" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" t="s">
+        <v>37</v>
+      </c>
+      <c r="B420" t="s">
+        <v>71</v>
+      </c>
+      <c r="C420" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" t="s">
+        <v>37</v>
+      </c>
+      <c r="B421" t="s">
+        <v>71</v>
+      </c>
+      <c r="C421" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" t="s">
+        <v>37</v>
+      </c>
+      <c r="B422" t="s">
+        <v>71</v>
+      </c>
+      <c r="C422" t="s">
+        <v>76</v>
+      </c>
+      <c r="D422" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" t="s">
+        <v>37</v>
+      </c>
+      <c r="B423" t="s">
+        <v>71</v>
+      </c>
+      <c r="C423" t="s">
+        <v>77</v>
+      </c>
+      <c r="D423" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" t="s">
+        <v>37</v>
+      </c>
+      <c r="B424" t="s">
+        <v>71</v>
+      </c>
+      <c r="C424" t="s">
+        <v>78</v>
+      </c>
+      <c r="D424" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" t="s">
+        <v>37</v>
+      </c>
+      <c r="B425" t="s">
+        <v>71</v>
+      </c>
+      <c r="C425" t="s">
+        <v>79</v>
+      </c>
+      <c r="D425" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426" t="s">
+        <v>37</v>
+      </c>
+      <c r="B426" t="s">
+        <v>71</v>
+      </c>
+      <c r="C426" t="s">
+        <v>80</v>
+      </c>
+      <c r="D426" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427" t="s">
+        <v>37</v>
+      </c>
+      <c r="B427" t="s">
+        <v>71</v>
+      </c>
+      <c r="C427" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428" t="s">
+        <v>37</v>
+      </c>
+      <c r="B428" t="s">
+        <v>71</v>
+      </c>
+      <c r="C428" t="s">
         <v>82</v>
+      </c>
+      <c r="D428" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429" t="s">
+        <v>37</v>
+      </c>
+      <c r="B429" t="s">
+        <v>71</v>
+      </c>
+      <c r="C429" t="s">
+        <v>83</v>
+      </c>
+      <c r="D429" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" t="s">
+        <v>37</v>
+      </c>
+      <c r="B430" t="s">
+        <v>71</v>
+      </c>
+      <c r="C430" t="s">
+        <v>84</v>
+      </c>
+      <c r="D430" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
